--- a/data/WP18/WP18_sachgebiete_FDP.xlsx
+++ b/data/WP18/WP18_sachgebiete_FDP.xlsx
@@ -949,10 +949,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>30.974025974026</v>
+        <v>30.9102564102564</v>
       </c>
       <c r="E12" t="n">
         <v>38</v>
@@ -3266,13 +3266,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A57DC73F-59AB-41B9-8528-690274249CEA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00E8C420-1BFF-4EB2-8EA3-D07258652D4F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65A4E2B5-14B9-43C9-9EFE-9C9A324F6FDE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03BAD070-87EE-4ABF-A998-BF8488CD595F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACA8750D-F627-450E-BFFC-05E1386783E4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C31A302-4A78-43D4-A5A9-E08C9465A6DD}"/>
 </file>
--- a/data/WP18/WP18_sachgebiete_FDP.xlsx
+++ b/data/WP18/WP18_sachgebiete_FDP.xlsx
@@ -446,7 +446,7 @@
         <v>30.0239520958084</v>
       </c>
       <c r="E2" t="n">
-        <v>108</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3">
@@ -463,7 +463,7 @@
         <v>39.6273291925466</v>
       </c>
       <c r="E3" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4">
@@ -480,7 +480,7 @@
         <v>30.3333333333333</v>
       </c>
       <c r="E4" t="n">
-        <v>84</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5">
@@ -497,7 +497,7 @@
         <v>36.9405940594059</v>
       </c>
       <c r="E5" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6">
@@ -514,7 +514,7 @@
         <v>35.050505050505</v>
       </c>
       <c r="E6" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7">
@@ -531,7 +531,7 @@
         <v>33.7878787878788</v>
       </c>
       <c r="E7" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8">
@@ -548,7 +548,7 @@
         <v>28.7391304347826</v>
       </c>
       <c r="E8" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
@@ -565,7 +565,7 @@
         <v>47.9230769230769</v>
       </c>
       <c r="E9" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10">
@@ -582,7 +582,7 @@
         <v>34.0705882352941</v>
       </c>
       <c r="E10" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11">
@@ -599,7 +599,7 @@
         <v>43.7179487179487</v>
       </c>
       <c r="E11" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12">
@@ -633,7 +633,7 @@
         <v>30.7297297297297</v>
       </c>
       <c r="E13" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
@@ -650,7 +650,7 @@
         <v>31.5714285714286</v>
       </c>
       <c r="E14" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15">
@@ -667,7 +667,7 @@
         <v>30.8</v>
       </c>
       <c r="E15" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16">
@@ -684,7 +684,7 @@
         <v>34.76</v>
       </c>
       <c r="E16" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17">
@@ -701,7 +701,7 @@
         <v>38.5</v>
       </c>
       <c r="E17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18">
@@ -718,7 +718,7 @@
         <v>34.5</v>
       </c>
       <c r="E18" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19">
@@ -752,7 +752,7 @@
         <v>44.8684210526316</v>
       </c>
       <c r="E20" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21">
@@ -769,7 +769,7 @@
         <v>29.6842105263158</v>
       </c>
       <c r="E21" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1006,13 +1006,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EC4653A-7D54-442E-931E-30CBBAEBBE3A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D47DCEB2-DE43-4B43-807A-6CF78CFDECAE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B13D33D-8A3F-4924-9915-14320C508C70}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{99E26768-62E1-47F9-802D-D3196C4C3294}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D211A3ED-4A71-41E6-8F2D-F3CDF99E6B42}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C42056E-9298-40DC-8BED-0A2E6BAE5256}"/>
 </file>